--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_nuble_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_nuble_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-04 13:58</t>
+    <t xml:space="preserve">2026-08-07 06:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_nuble_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_nuble_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07 06:24</t>
+    <t xml:space="preserve">2026-08-13 12:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_nuble_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_nuble_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-13 12:44</t>
+    <t xml:space="preserve">2026-08-19 11:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_nuble_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_nuble_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 11:44</t>
+    <t xml:space="preserve">2026-08-28 10:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_nuble_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_nuble_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 10:54</t>
+    <t xml:space="preserve">2026-09-01 11:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_nuble_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_nuble_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 11:23</t>
+    <t xml:space="preserve">2026-09-04 20:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_nuble_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_nuble_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04 20:00</t>
+    <t xml:space="preserve">2026-09-06 16:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_nuble_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_nuble_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 16:32</t>
+    <t xml:space="preserve">2026-09-08 11:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
